--- a/Employee_Reports_wi48/Abdunaser Ahmed Aragaw Q0042.xlsx
+++ b/Employee_Reports_wi48/Abdunaser Ahmed Aragaw Q0042.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -606,11 +606,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -643,11 +643,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
